--- a/Output/logit_post_x_key_coefficients.xlsx
+++ b/Output/logit_post_x_key_coefficients.xlsx
@@ -32,85 +32,85 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">1.065 (0.068)</t>
+    <t xml:space="preserve">1.072 (0.066)</t>
   </si>
   <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">1.060 (0.079)</t>
+    <t xml:space="preserve">1.055 (0.074)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_educ</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962 (0.064)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965 (0.072)</t>
+    <t xml:space="preserve">0.963 (0.065)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971 (0.073)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_izq_der</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750*** (0.080)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691*** (0.085)</t>
+    <t xml:space="preserve">0.723*** (0.081)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683*** (0.088)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_desempleado</t>
   </si>
   <si>
-    <t xml:space="preserve">49.687 (120.812)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.608 (151.656)</t>
+    <t xml:space="preserve">41.451 (107.897)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.697 (98.743)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_en_pareja</t>
   </si>
   <si>
-    <t xml:space="preserve">1.242 (1.266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954 (1.025)</t>
+    <t xml:space="preserve">1.038 (1.132)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809 (0.931)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_hombre</t>
   </si>
   <si>
-    <t xml:space="preserve">26.689 (163.617)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.111 (369.531)</t>
+    <t xml:space="preserve">22.430 (141.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.211 (537.383)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_interes_pol_mucho</t>
   </si>
   <si>
-    <t xml:space="preserve">4.933 (5.885)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.019 (6.569)</t>
+    <t xml:space="preserve">5.678 (6.954)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.906 (8.028)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_rural</t>
   </si>
   <si>
-    <t xml:space="preserve">0.894 (0.253)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874 (0.267)</t>
+    <t xml:space="preserve">0.836 (0.230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811 (0.251)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680 (1.040)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688 (1.188)</t>
+    <t xml:space="preserve">0.537 (0.867)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629 (1.118)</t>
   </si>
 </sst>
 </file>

--- a/Output/logit_post_x_key_coefficients.xlsx
+++ b/Output/logit_post_x_key_coefficients.xlsx
@@ -95,15 +95,6 @@
     <t xml:space="preserve">5.906 (8.028)</t>
   </si>
   <si>
-    <t xml:space="preserve">mun_pre_all_share_rural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836 (0.230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811 (0.251)</t>
-  </si>
-  <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
   </si>
   <si>
@@ -111,6 +102,15 @@
   </si>
   <si>
     <t xml:space="preserve">0.629 (1.118)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popdensgeo2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993 (0.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994 (0.028)</t>
   </si>
 </sst>
 </file>
@@ -688,7 +688,7 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="19">
@@ -702,7 +702,7 @@
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
   </sheetData>
